--- a/LLM_Extraction_and_CrossCritique/interactive-table/SQL_Results_Cat3_Working_Query.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/SQL_Results_Cat3_Working_Query.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E580F064-C127-4B94-819C-F40A0A65F1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF441875-3AA7-46A1-B7DD-582F1E028689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -4424,7 +4424,7 @@
     <col min="7" max="7" width="61" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4444,7 +4444,10 @@
         <v>975</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -4464,7 +4467,10 @@
         <v>977</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -4484,7 +4490,10 @@
         <v>979</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -4504,7 +4513,10 @@
         <v>981</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -4524,7 +4536,10 @@
         <v>983</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -4544,7 +4559,10 @@
         <v>985</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -4564,7 +4582,10 @@
         <v>987</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -4584,7 +4605,10 @@
         <v>989</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -4604,7 +4628,10 @@
         <v>990</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
@@ -4624,7 +4651,10 @@
         <v>992</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
         <v>23</v>
       </c>
@@ -4644,7 +4674,10 @@
         <v>983</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -4664,7 +4697,10 @@
         <v>987</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -4684,7 +4720,10 @@
         <v>994</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
       <c r="B14" t="s">
         <v>29</v>
       </c>
@@ -4704,7 +4743,10 @@
         <v>983</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
@@ -4724,7 +4766,10 @@
         <v>995</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
@@ -4744,7 +4789,10 @@
         <v>997</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -4764,7 +4812,10 @@
         <v>983</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
@@ -4784,7 +4835,10 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -4804,7 +4858,10 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
       <c r="B20" t="s">
         <v>41</v>
       </c>
@@ -4824,7 +4881,10 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
       <c r="B21" t="s">
         <v>43</v>
       </c>
@@ -4844,7 +4904,10 @@
         <v>983</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
       <c r="B22" t="s">
         <v>45</v>
       </c>
@@ -4864,7 +4927,10 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
       <c r="B23" t="s">
         <v>47</v>
       </c>
@@ -4884,7 +4950,10 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
       <c r="B24" t="s">
         <v>49</v>
       </c>
@@ -4904,7 +4973,10 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
       <c r="B25" t="s">
         <v>51</v>
       </c>
@@ -4924,7 +4996,10 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
       <c r="B26" t="s">
         <v>53</v>
       </c>
@@ -4944,7 +5019,10 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
       <c r="B27" t="s">
         <v>55</v>
       </c>
@@ -4964,7 +5042,10 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
       <c r="B28" t="s">
         <v>57</v>
       </c>
@@ -4984,7 +5065,10 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
       <c r="B29" t="s">
         <v>59</v>
       </c>
@@ -5004,7 +5088,10 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
       <c r="B30" t="s">
         <v>61</v>
       </c>
@@ -5024,7 +5111,10 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
       <c r="B31" t="s">
         <v>63</v>
       </c>
@@ -5044,7 +5134,10 @@
         <v>985</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
       <c r="B32" t="s">
         <v>65</v>
       </c>
@@ -5064,7 +5157,10 @@
         <v>994</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
       <c r="B33" t="s">
         <v>67</v>
       </c>
@@ -5084,7 +5180,10 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
       <c r="B34" t="s">
         <v>69</v>
       </c>
@@ -5104,7 +5203,10 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
       <c r="B35" t="s">
         <v>71</v>
       </c>
@@ -5124,7 +5226,10 @@
         <v>981</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
       <c r="B36" t="s">
         <v>73</v>
       </c>
@@ -5144,7 +5249,10 @@
         <v>977</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
       <c r="B37" t="s">
         <v>75</v>
       </c>
@@ -5164,7 +5272,10 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
       <c r="B38" t="s">
         <v>77</v>
       </c>
@@ -5184,7 +5295,10 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
       <c r="B39" t="s">
         <v>79</v>
       </c>
@@ -5204,7 +5318,10 @@
         <v>987</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
       <c r="B40" t="s">
         <v>81</v>
       </c>
@@ -5224,7 +5341,10 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" t="s">
         <v>83</v>
       </c>
@@ -5244,7 +5364,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" t="s">
         <v>85</v>
       </c>
@@ -5264,7 +5387,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="B43" t="s">
         <v>87</v>
       </c>
@@ -5284,7 +5410,10 @@
         <v>995</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
       <c r="B44" t="s">
         <v>89</v>
       </c>
@@ -5304,7 +5433,10 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
       <c r="B45" t="s">
         <v>91</v>
       </c>
@@ -5324,7 +5456,10 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
       <c r="B46" t="s">
         <v>93</v>
       </c>
@@ -5344,7 +5479,10 @@
         <v>985</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
       <c r="B47" t="s">
         <v>95</v>
       </c>
@@ -5364,7 +5502,10 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
       <c r="B48" t="s">
         <v>97</v>
       </c>
@@ -5384,7 +5525,10 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
       <c r="B49" t="s">
         <v>99</v>
       </c>
@@ -5404,7 +5548,10 @@
         <v>987</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
       <c r="B50" t="s">
         <v>101</v>
       </c>
@@ -5424,7 +5571,10 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
       <c r="B51" t="s">
         <v>103</v>
       </c>
@@ -5444,7 +5594,10 @@
         <v>979</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
       <c r="B52" t="s">
         <v>105</v>
       </c>
@@ -5464,7 +5617,10 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
       <c r="B53" t="s">
         <v>107</v>
       </c>
@@ -5484,7 +5640,10 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
@@ -5504,7 +5663,10 @@
         <v>995</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
       <c r="B55" t="s">
         <v>111</v>
       </c>
@@ -5524,7 +5686,10 @@
         <v>987</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
       <c r="B56" t="s">
         <v>113</v>
       </c>
@@ -5544,7 +5709,10 @@
         <v>997</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
       <c r="B57" t="s">
         <v>115</v>
       </c>
@@ -5564,7 +5732,10 @@
         <v>989</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
       <c r="B58" t="s">
         <v>117</v>
       </c>
@@ -5584,7 +5755,10 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
       <c r="B59" t="s">
         <v>119</v>
       </c>
@@ -5604,7 +5778,10 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
       <c r="B60" t="s">
         <v>121</v>
       </c>
@@ -5624,7 +5801,10 @@
         <v>981</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
       <c r="B61" t="s">
         <v>123</v>
       </c>
@@ -5644,7 +5824,10 @@
         <v>987</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
       <c r="B62" t="s">
         <v>125</v>
       </c>
@@ -5664,7 +5847,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
       <c r="B63" t="s">
         <v>127</v>
       </c>
@@ -5684,7 +5870,10 @@
         <v>992</v>
       </c>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
       <c r="B64" t="s">
         <v>129</v>
       </c>
@@ -5704,7 +5893,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
       <c r="B65" t="s">
         <v>131</v>
       </c>
@@ -5724,7 +5916,10 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
       <c r="B66" t="s">
         <v>133</v>
       </c>
@@ -5744,7 +5939,10 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
       <c r="B67" t="s">
         <v>135</v>
       </c>
@@ -5764,7 +5962,10 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
       <c r="B68" t="s">
         <v>137</v>
       </c>
@@ -5784,7 +5985,10 @@
         <v>979</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
       <c r="B69" t="s">
         <v>139</v>
       </c>
@@ -5804,7 +6008,10 @@
         <v>985</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
       <c r="B70" t="s">
         <v>141</v>
       </c>
@@ -5824,7 +6031,10 @@
         <v>997</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
       <c r="B71" t="s">
         <v>143</v>
       </c>
@@ -5844,7 +6054,10 @@
         <v>977</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
       <c r="B72" t="s">
         <v>145</v>
       </c>
@@ -5864,7 +6077,10 @@
         <v>983</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
       <c r="B73" t="s">
         <v>147</v>
       </c>
@@ -5884,7 +6100,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
       <c r="B74" t="s">
         <v>149</v>
       </c>
@@ -5904,7 +6123,10 @@
         <v>985</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
       <c r="B75" t="s">
         <v>151</v>
       </c>
@@ -5924,7 +6146,10 @@
         <v>979</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
       <c r="B76" t="s">
         <v>153</v>
       </c>
@@ -5944,7 +6169,10 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
       <c r="B77" t="s">
         <v>155</v>
       </c>
@@ -5964,7 +6192,10 @@
         <v>995</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
       <c r="B78" t="s">
         <v>157</v>
       </c>
@@ -5984,7 +6215,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
       <c r="B79" t="s">
         <v>159</v>
       </c>
@@ -6004,7 +6238,10 @@
         <v>997</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
       <c r="B80" t="s">
         <v>161</v>
       </c>
@@ -6024,7 +6261,10 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
       <c r="B81" t="s">
         <v>163</v>
       </c>
@@ -6044,7 +6284,10 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
       <c r="B82" t="s">
         <v>165</v>
       </c>
@@ -6064,7 +6307,10 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
       <c r="B83" t="s">
         <v>167</v>
       </c>
@@ -6084,7 +6330,10 @@
         <v>977</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
       <c r="B84" t="s">
         <v>169</v>
       </c>
@@ -6104,7 +6353,10 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
       <c r="B85" t="s">
         <v>171</v>
       </c>
@@ -6124,7 +6376,10 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
       <c r="B86" t="s">
         <v>173</v>
       </c>
@@ -6144,7 +6399,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
       <c r="B87" t="s">
         <v>175</v>
       </c>
@@ -6164,7 +6422,10 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
       <c r="B88" t="s">
         <v>177</v>
       </c>
@@ -6184,7 +6445,10 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
       <c r="B89" t="s">
         <v>179</v>
       </c>
@@ -6204,7 +6468,10 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
       <c r="B90" t="s">
         <v>181</v>
       </c>
@@ -6224,7 +6491,10 @@
         <v>995</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
       <c r="B91" t="s">
         <v>183</v>
       </c>
@@ -6244,7 +6514,10 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
       <c r="B92" t="s">
         <v>185</v>
       </c>
@@ -6264,7 +6537,10 @@
         <v>979</v>
       </c>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
       <c r="B93" t="s">
         <v>187</v>
       </c>
@@ -6284,7 +6560,10 @@
         <v>981</v>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
       <c r="B94" t="s">
         <v>189</v>
       </c>
@@ -6304,7 +6583,10 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>94</v>
+      </c>
       <c r="B95" t="s">
         <v>191</v>
       </c>
@@ -6324,7 +6606,10 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>95</v>
+      </c>
       <c r="B96" t="s">
         <v>193</v>
       </c>
@@ -6345,6 +6630,9 @@
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
       <c r="B97" t="s">
         <v>195</v>
       </c>
@@ -6365,6 +6653,9 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
       <c r="B98" t="s">
         <v>197</v>
       </c>
@@ -6385,6 +6676,9 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
       <c r="B99" t="s">
         <v>199</v>
       </c>
@@ -6405,6 +6699,9 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
       <c r="B100" t="s">
         <v>201</v>
       </c>
@@ -6425,6 +6722,9 @@
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
       <c r="B101" t="s">
         <v>203</v>
       </c>

--- a/LLM_Extraction_and_CrossCritique/interactive-table/SQL_Results_Cat3_Working_Query.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/SQL_Results_Cat3_Working_Query.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\OneDrive\Desktop\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF441875-3AA7-46A1-B7DD-582F1E028689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F10F47B-737A-47F5-AFEA-A772DB91216C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -4414,17 +4414,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE9FACD-1DBE-4891-9647-5699A06CB061}">
   <dimension ref="A1:G501"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="167.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="201.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="167.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="201.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="61" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7342,7 +7342,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8078,7 +8078,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -8561,7 +8561,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8584,7 +8584,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -8860,7 +8860,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -9044,7 +9044,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>396</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
         <v>398</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
         <v>400</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
         <v>402</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
         <v>404</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
         <v>406</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>408</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
         <v>410</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>411</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
         <v>413</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
         <v>415</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
         <v>417</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
         <v>419</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
         <v>421</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
         <v>423</v>
       </c>
@@ -9344,7 +9344,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
         <v>425</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
         <v>427</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B219" t="s">
         <v>429</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B220" t="s">
         <v>431</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B221" t="s">
         <v>433</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B222" t="s">
         <v>435</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B223" t="s">
         <v>437</v>
       </c>
@@ -9484,7 +9484,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B224" t="s">
         <v>439</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B225" t="s">
         <v>441</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
         <v>443</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
         <v>445</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="228" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
         <v>447</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
         <v>449</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B230" t="s">
         <v>451</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="231" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B231" t="s">
         <v>452</v>
       </c>
@@ -9644,7 +9644,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>454</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>456</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>458</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="235" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
         <v>459</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="236" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B236" t="s">
         <v>461</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="237" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B237" t="s">
         <v>463</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="238" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B238" t="s">
         <v>465</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="239" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
         <v>467</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="240" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B240" t="s">
         <v>469</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
         <v>471</v>
       </c>
@@ -9844,7 +9844,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="242" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
         <v>473</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="243" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B243" t="s">
         <v>475</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="244" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B244" t="s">
         <v>477</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="245" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B245" t="s">
         <v>478</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="246" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B246" t="s">
         <v>480</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="247" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B247" t="s">
         <v>482</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="248" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
         <v>484</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="249" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B249" t="s">
         <v>485</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="250" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B250" t="s">
         <v>487</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="251" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B251" t="s">
         <v>489</v>
       </c>
@@ -10044,7 +10044,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="252" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B252" t="s">
         <v>491</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="253" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B253" t="s">
         <v>493</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="254" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B254" t="s">
         <v>495</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="255" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
         <v>497</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="256" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B256" t="s">
         <v>499</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="257" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
         <v>501</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="258" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B258" t="s">
         <v>502</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="259" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B259" t="s">
         <v>504</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="260" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
         <v>506</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="261" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B261" t="s">
         <v>508</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="262" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B262" t="s">
         <v>510</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="263" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B263" t="s">
         <v>512</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="264" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B264" t="s">
         <v>514</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="265" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B265" t="s">
         <v>516</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="266" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B266" t="s">
         <v>518</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="267" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B267" t="s">
         <v>520</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="268" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B268" t="s">
         <v>522</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="269" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B269" t="s">
         <v>524</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="270" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B270" t="s">
         <v>526</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="271" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B271" t="s">
         <v>528</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="272" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B272" t="s">
         <v>530</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="273" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B273" t="s">
         <v>532</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="274" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B274" t="s">
         <v>533</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="275" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B275" t="s">
         <v>535</v>
       </c>
@@ -10524,7 +10524,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="276" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B276" t="s">
         <v>537</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="277" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B277" t="s">
         <v>539</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="278" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B278" t="s">
         <v>541</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="279" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B279" t="s">
         <v>543</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="280" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B280" t="s">
         <v>545</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="281" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B281" t="s">
         <v>547</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="282" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B282" t="s">
         <v>549</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="283" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B283" t="s">
         <v>551</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="284" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B284" t="s">
         <v>553</v>
       </c>
@@ -10704,7 +10704,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="285" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B285" t="s">
         <v>555</v>
       </c>
@@ -10724,7 +10724,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="286" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
         <v>557</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="287" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B287" t="s">
         <v>559</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="288" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B288" t="s">
         <v>561</v>
       </c>
@@ -10784,7 +10784,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="289" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B289" t="s">
         <v>563</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="290" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B290" t="s">
         <v>565</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="291" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B291" t="s">
         <v>567</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="292" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B292" t="s">
         <v>569</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="293" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B293" t="s">
         <v>571</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="294" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B294" t="s">
         <v>573</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="295" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B295" t="s">
         <v>575</v>
       </c>
@@ -10924,7 +10924,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="296" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B296" t="s">
         <v>577</v>
       </c>
@@ -10944,7 +10944,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="297" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B297" t="s">
         <v>578</v>
       </c>
@@ -10964,7 +10964,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="298" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B298" t="s">
         <v>580</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="299" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B299" t="s">
         <v>582</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="300" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B300" t="s">
         <v>584</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="301" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B301" t="s">
         <v>586</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="302" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B302" t="s">
         <v>588</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="303" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B303" t="s">
         <v>590</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="304" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B304" t="s">
         <v>592</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="305" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B305" t="s">
         <v>594</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="306" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B306" t="s">
         <v>596</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="307" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B307" t="s">
         <v>598</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="308" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B308" t="s">
         <v>600</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="309" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B309" t="s">
         <v>602</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="310" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B310" t="s">
         <v>604</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="311" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B311" t="s">
         <v>606</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="312" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B312" t="s">
         <v>608</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="313" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B313" t="s">
         <v>610</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="314" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B314" t="s">
         <v>612</v>
       </c>
@@ -11304,7 +11304,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="315" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B315" t="s">
         <v>614</v>
       </c>
@@ -11324,7 +11324,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="316" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B316" t="s">
         <v>616</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="317" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B317" t="s">
         <v>618</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="318" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B318" t="s">
         <v>620</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="319" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B319" t="s">
         <v>622</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="320" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B320" t="s">
         <v>624</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="321" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B321" t="s">
         <v>626</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="322" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B322" t="s">
         <v>628</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="323" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B323" t="s">
         <v>630</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="324" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B324" t="s">
         <v>632</v>
       </c>
@@ -11504,7 +11504,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="325" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B325" t="s">
         <v>634</v>
       </c>
@@ -11524,7 +11524,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="326" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B326" t="s">
         <v>636</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="327" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B327" t="s">
         <v>638</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="328" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B328" t="s">
         <v>640</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="329" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B329" t="s">
         <v>642</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="330" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B330" t="s">
         <v>643</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="331" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B331" t="s">
         <v>645</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="332" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B332" t="s">
         <v>647</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="333" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B333" t="s">
         <v>649</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="334" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B334" t="s">
         <v>651</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="335" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B335" t="s">
         <v>652</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="336" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B336" t="s">
         <v>654</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="337" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B337" t="s">
         <v>656</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="338" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B338" t="s">
         <v>658</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="339" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B339" t="s">
         <v>660</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="340" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B340" t="s">
         <v>661</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="341" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B341" t="s">
         <v>663</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="342" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B342" t="s">
         <v>665</v>
       </c>
@@ -11864,7 +11864,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="343" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B343" t="s">
         <v>667</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="344" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B344" t="s">
         <v>669</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="345" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B345" t="s">
         <v>671</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="346" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B346" t="s">
         <v>672</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="347" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B347" t="s">
         <v>673</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="348" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B348" t="s">
         <v>675</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="349" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B349" t="s">
         <v>677</v>
       </c>
@@ -12004,7 +12004,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="350" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B350" t="s">
         <v>679</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="351" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B351" t="s">
         <v>681</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="352" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B352" t="s">
         <v>683</v>
       </c>
@@ -12064,7 +12064,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="353" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B353" t="s">
         <v>685</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="354" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B354" t="s">
         <v>687</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="355" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B355" t="s">
         <v>689</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="356" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B356" t="s">
         <v>691</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="357" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B357" t="s">
         <v>693</v>
       </c>
@@ -12164,7 +12164,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="358" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B358" t="s">
         <v>695</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="359" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B359" t="s">
         <v>697</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="360" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B360" t="s">
         <v>699</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="361" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B361" t="s">
         <v>701</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="362" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B362" t="s">
         <v>703</v>
       </c>
@@ -12264,7 +12264,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="363" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B363" t="s">
         <v>704</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="364" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B364" t="s">
         <v>706</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="365" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B365" t="s">
         <v>708</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="366" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B366" t="s">
         <v>710</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="367" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B367" t="s">
         <v>712</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="368" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B368" t="s">
         <v>714</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="369" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B369" t="s">
         <v>716</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="370" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B370" t="s">
         <v>718</v>
       </c>
@@ -12424,7 +12424,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="371" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B371" t="s">
         <v>720</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="372" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B372" t="s">
         <v>721</v>
       </c>
@@ -12464,7 +12464,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="373" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B373" t="s">
         <v>723</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="374" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B374" t="s">
         <v>725</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="375" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B375" t="s">
         <v>727</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="376" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B376" t="s">
         <v>729</v>
       </c>
@@ -12544,7 +12544,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="377" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B377" t="s">
         <v>731</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="378" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B378" t="s">
         <v>733</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="379" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B379" t="s">
         <v>735</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="380" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B380" t="s">
         <v>737</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="381" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B381" t="s">
         <v>739</v>
       </c>
@@ -12644,7 +12644,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="382" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B382" t="s">
         <v>741</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="383" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B383" t="s">
         <v>742</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="384" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B384" t="s">
         <v>744</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="385" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B385" t="s">
         <v>746</v>
       </c>
@@ -12724,7 +12724,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="386" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B386" t="s">
         <v>748</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="387" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B387" t="s">
         <v>750</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="388" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B388" t="s">
         <v>752</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="389" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B389" t="s">
         <v>754</v>
       </c>
@@ -12804,7 +12804,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="390" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B390" t="s">
         <v>756</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="391" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B391" t="s">
         <v>758</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="392" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B392" t="s">
         <v>760</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="393" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B393" t="s">
         <v>762</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="394" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B394" t="s">
         <v>764</v>
       </c>
@@ -12904,7 +12904,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="395" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B395" t="s">
         <v>766</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="396" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B396" t="s">
         <v>768</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="397" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B397" t="s">
         <v>770</v>
       </c>
@@ -12964,7 +12964,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="398" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B398" t="s">
         <v>772</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="399" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B399" t="s">
         <v>774</v>
       </c>
@@ -13004,7 +13004,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="400" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B400" t="s">
         <v>776</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="401" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B401" t="s">
         <v>778</v>
       </c>
@@ -13044,7 +13044,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="402" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B402" t="s">
         <v>780</v>
       </c>
@@ -13064,7 +13064,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="403" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B403" t="s">
         <v>782</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="404" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B404" t="s">
         <v>784</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="405" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B405" t="s">
         <v>786</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="406" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B406" t="s">
         <v>788</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="407" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B407" t="s">
         <v>790</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="408" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B408" t="s">
         <v>792</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="409" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B409" t="s">
         <v>794</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="410" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B410" t="s">
         <v>796</v>
       </c>
@@ -13224,7 +13224,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="411" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B411" t="s">
         <v>798</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="412" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B412" t="s">
         <v>800</v>
       </c>
@@ -13264,7 +13264,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="413" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B413" t="s">
         <v>802</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="414" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B414" t="s">
         <v>804</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="415" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B415" t="s">
         <v>806</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="416" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B416" t="s">
         <v>808</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="417" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B417" t="s">
         <v>810</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="418" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B418" t="s">
         <v>812</v>
       </c>
@@ -13384,7 +13384,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="419" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B419" t="s">
         <v>814</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="420" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B420" t="s">
         <v>816</v>
       </c>
@@ -13424,7 +13424,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="421" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B421" t="s">
         <v>818</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="422" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B422" t="s">
         <v>820</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="423" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B423" t="s">
         <v>822</v>
       </c>
@@ -13484,7 +13484,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="424" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B424" t="s">
         <v>824</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="425" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B425" t="s">
         <v>826</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="426" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B426" t="s">
         <v>828</v>
       </c>
@@ -13544,7 +13544,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="427" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B427" t="s">
         <v>830</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="428" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B428" t="s">
         <v>832</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="429" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B429" t="s">
         <v>834</v>
       </c>
@@ -13604,7 +13604,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="430" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B430" t="s">
         <v>836</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="431" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B431" t="s">
         <v>838</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="432" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B432" t="s">
         <v>840</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="433" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B433" t="s">
         <v>842</v>
       </c>
@@ -13684,7 +13684,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="434" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B434" t="s">
         <v>844</v>
       </c>
@@ -13704,7 +13704,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="435" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B435" t="s">
         <v>846</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="436" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B436" t="s">
         <v>848</v>
       </c>
@@ -13744,7 +13744,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="437" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B437" t="s">
         <v>849</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="438" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B438" t="s">
         <v>851</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="439" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B439" t="s">
         <v>853</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="440" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B440" t="s">
         <v>855</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="441" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B441" t="s">
         <v>857</v>
       </c>
@@ -13844,7 +13844,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="442" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B442" t="s">
         <v>859</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="443" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B443" t="s">
         <v>861</v>
       </c>
@@ -13884,7 +13884,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="444" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B444" t="s">
         <v>863</v>
       </c>
@@ -13904,7 +13904,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="445" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B445" t="s">
         <v>865</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="446" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B446" t="s">
         <v>867</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="447" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B447" t="s">
         <v>869</v>
       </c>
@@ -13964,7 +13964,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="448" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B448" t="s">
         <v>871</v>
       </c>
@@ -13984,7 +13984,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="449" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B449" t="s">
         <v>873</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="450" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B450" t="s">
         <v>875</v>
       </c>
@@ -14024,7 +14024,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="451" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B451" t="s">
         <v>877</v>
       </c>
@@ -14044,7 +14044,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="452" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B452" t="s">
         <v>879</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="453" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B453" t="s">
         <v>881</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="454" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B454" t="s">
         <v>883</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="455" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B455" t="s">
         <v>885</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="456" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B456" t="s">
         <v>887</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="457" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B457" t="s">
         <v>888</v>
       </c>
@@ -14164,7 +14164,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="458" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B458" t="s">
         <v>889</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="459" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B459" t="s">
         <v>891</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="460" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B460" t="s">
         <v>893</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="461" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B461" t="s">
         <v>895</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="462" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B462" t="s">
         <v>897</v>
       </c>
@@ -14264,7 +14264,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="463" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B463" t="s">
         <v>899</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="464" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B464" t="s">
         <v>901</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="465" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B465" t="s">
         <v>903</v>
       </c>
@@ -14324,7 +14324,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="466" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B466" t="s">
         <v>905</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="467" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B467" t="s">
         <v>907</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="468" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B468" t="s">
         <v>909</v>
       </c>
@@ -14384,7 +14384,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="469" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B469" t="s">
         <v>911</v>
       </c>
@@ -14404,7 +14404,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="470" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B470" t="s">
         <v>912</v>
       </c>
@@ -14424,7 +14424,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="471" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B471" t="s">
         <v>914</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="472" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B472" t="s">
         <v>916</v>
       </c>
@@ -14464,7 +14464,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="473" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B473" t="s">
         <v>918</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="474" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B474" t="s">
         <v>920</v>
       </c>
@@ -14504,7 +14504,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="475" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B475" t="s">
         <v>922</v>
       </c>
@@ -14524,7 +14524,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="476" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B476" t="s">
         <v>924</v>
       </c>
@@ -14544,7 +14544,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="477" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B477" t="s">
         <v>926</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="478" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B478" t="s">
         <v>928</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="479" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B479" t="s">
         <v>930</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="480" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B480" t="s">
         <v>932</v>
       </c>
@@ -14624,7 +14624,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="481" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B481" t="s">
         <v>934</v>
       </c>
@@ -14644,7 +14644,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="482" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B482" t="s">
         <v>936</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="483" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B483" t="s">
         <v>938</v>
       </c>
@@ -14684,7 +14684,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="484" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B484" t="s">
         <v>940</v>
       </c>
@@ -14704,7 +14704,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="485" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B485" t="s">
         <v>942</v>
       </c>
@@ -14724,7 +14724,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="486" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B486" t="s">
         <v>944</v>
       </c>
@@ -14744,7 +14744,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="487" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B487" t="s">
         <v>945</v>
       </c>
@@ -14764,7 +14764,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="488" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B488" t="s">
         <v>947</v>
       </c>
@@ -14784,7 +14784,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="489" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B489" t="s">
         <v>949</v>
       </c>
@@ -14804,7 +14804,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="490" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B490" t="s">
         <v>951</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="491" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B491" t="s">
         <v>953</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="492" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B492" t="s">
         <v>955</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="493" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B493" t="s">
         <v>957</v>
       </c>
@@ -14884,7 +14884,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="494" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B494" t="s">
         <v>959</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="495" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B495" t="s">
         <v>961</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="496" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B496" t="s">
         <v>963</v>
       </c>
@@ -14944,7 +14944,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="497" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B497" t="s">
         <v>965</v>
       </c>
@@ -14964,7 +14964,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="498" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B498" t="s">
         <v>967</v>
       </c>
@@ -14984,7 +14984,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="499" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B499" t="s">
         <v>969</v>
       </c>
@@ -15004,7 +15004,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="500" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B500" t="s">
         <v>971</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="501" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B501" t="s">
         <v>972</v>
       </c>
